--- a/Resources/ExportCuttingSpanishHose.xlsx
+++ b/Resources/ExportCuttingSpanishHose.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompanyProjects\spanish-hose-program\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\TechlinkProjects\techlink-new-all-in-one\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{008E8157-4518-4A5E-91B3-95533FD3C6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81F638E-33A9-450B-8348-6339C790CFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>数量</t>
   </si>
@@ -53,11 +53,19 @@
  Số tấm</t>
   </si>
   <si>
-    <t>料层代码
-Mã lớp liệu</t>
+    <t>Báo biểu khu vực ống Tây Ban Nha</t>
   </si>
   <si>
-    <t>Báo biểu khu vực ống Tây Ban Nha</t>
+    <t>原材料代码
+Mã nguyên liệu</t>
+  </si>
+  <si>
+    <t>规格
+Quy cách</t>
+  </si>
+  <si>
+    <t>材料的类型
+Loại nguyên liệu</t>
   </si>
 </sst>
 </file>
@@ -451,20 +459,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G453"/>
+  <dimension ref="A1:I453"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.5546875" style="3" customWidth="1"/>
-    <col min="2" max="3" width="18.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.77734375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="28" style="3" customWidth="1"/>
+    <col min="2" max="5" width="18.33203125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="19.77734375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="25.21875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -472,8 +480,10 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-    </row>
-    <row r="2" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -481,33 +491,41 @@
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -515,8 +533,10 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -524,8 +544,10 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -533,8 +555,10 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -542,8 +566,10 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -551,8 +577,10 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -560,8 +588,10 @@
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -569,8 +599,10 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -578,8 +610,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -587,8 +621,10 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -596,8 +632,10 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -605,8 +643,10 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -614,8 +654,10 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -623,8 +665,10 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -632,8 +676,10 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -641,8 +687,10 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -650,8 +698,10 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -659,8 +709,10 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -668,8 +720,10 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -677,8 +731,10 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -686,8 +742,10 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -695,8 +753,10 @@
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -704,8 +764,10 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -713,8 +775,10 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -722,8 +786,10 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -731,8 +797,10 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -740,8 +808,10 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -749,8 +819,10 @@
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -758,8 +830,10 @@
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -767,8 +841,10 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -776,8 +852,10 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -785,8 +863,10 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -794,8 +874,10 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -803,8 +885,10 @@
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -812,8 +896,10 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -821,8 +907,10 @@
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -830,8 +918,10 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -839,8 +929,10 @@
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -848,8 +940,10 @@
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -857,8 +951,10 @@
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -866,8 +962,10 @@
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -875,8 +973,10 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -884,8 +984,10 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -893,8 +995,10 @@
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -902,8 +1006,10 @@
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -911,8 +1017,10 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -920,8 +1028,10 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -929,8 +1039,10 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -938,8 +1050,10 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -947,8 +1061,10 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -956,8 +1072,10 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -965,8 +1083,10 @@
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -974,8 +1094,10 @@
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -983,8 +1105,10 @@
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -992,8 +1116,10 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -1001,8 +1127,10 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -1010,8 +1138,10 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -1019,8 +1149,10 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -1028,8 +1160,10 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -1037,8 +1171,10 @@
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1046,8 +1182,10 @@
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -1055,8 +1193,10 @@
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -1064,8 +1204,10 @@
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -1073,8 +1215,10 @@
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -1082,8 +1226,10 @@
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -1091,8 +1237,10 @@
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -1100,8 +1248,10 @@
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -1109,8 +1259,10 @@
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -1118,8 +1270,10 @@
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -1127,8 +1281,10 @@
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -1136,8 +1292,10 @@
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -1145,8 +1303,10 @@
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -1154,8 +1314,10 @@
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -1163,8 +1325,10 @@
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -1172,8 +1336,10 @@
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -1181,8 +1347,10 @@
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -1190,8 +1358,10 @@
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -1199,8 +1369,10 @@
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -1208,8 +1380,10 @@
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -1217,8 +1391,10 @@
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -1226,8 +1402,10 @@
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -1235,8 +1413,10 @@
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -1244,8 +1424,10 @@
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -1253,8 +1435,10 @@
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -1262,8 +1446,10 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -1271,8 +1457,10 @@
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -1280,8 +1468,10 @@
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -1289,8 +1479,10 @@
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -1298,8 +1490,10 @@
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -1307,8 +1501,10 @@
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -1316,8 +1512,10 @@
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -1325,8 +1523,10 @@
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -1334,8 +1534,10 @@
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -1343,8 +1545,10 @@
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -1352,8 +1556,10 @@
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -1361,8 +1567,10 @@
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -1370,8 +1578,10 @@
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -1379,8 +1589,10 @@
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -1388,8 +1600,10 @@
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -1397,8 +1611,10 @@
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -1406,8 +1622,10 @@
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -1415,8 +1633,10 @@
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -1424,8 +1644,10 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -1433,8 +1655,10 @@
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -1442,8 +1666,10 @@
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -1451,8 +1677,10 @@
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -1460,8 +1688,10 @@
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -1469,8 +1699,10 @@
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -1478,8 +1710,10 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -1487,8 +1721,10 @@
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -1496,8 +1732,10 @@
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -1505,8 +1743,10 @@
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -1514,8 +1754,10 @@
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -1523,8 +1765,10 @@
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -1532,8 +1776,10 @@
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -1541,8 +1787,10 @@
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -1550,8 +1798,10 @@
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -1559,8 +1809,10 @@
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -1568,8 +1820,10 @@
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -1577,8 +1831,10 @@
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -1586,8 +1842,10 @@
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -1595,8 +1853,10 @@
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -1604,8 +1864,10 @@
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -1613,8 +1875,10 @@
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -1622,8 +1886,10 @@
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -1631,8 +1897,10 @@
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H128" s="1"/>
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -1640,8 +1908,10 @@
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -1649,8 +1919,10 @@
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H130" s="1"/>
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -1658,8 +1930,10 @@
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H131" s="1"/>
+      <c r="I131" s="1"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -1667,8 +1941,10 @@
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H132" s="1"/>
+      <c r="I132" s="1"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -1676,8 +1952,10 @@
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H133" s="1"/>
+      <c r="I133" s="1"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -1685,8 +1963,10 @@
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H134" s="1"/>
+      <c r="I134" s="1"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -1694,8 +1974,10 @@
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H135" s="1"/>
+      <c r="I135" s="1"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -1703,8 +1985,10 @@
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H136" s="1"/>
+      <c r="I136" s="1"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -1712,8 +1996,10 @@
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H137" s="1"/>
+      <c r="I137" s="1"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -1721,8 +2007,10 @@
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H138" s="1"/>
+      <c r="I138" s="1"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -1730,8 +2018,10 @@
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H139" s="1"/>
+      <c r="I139" s="1"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -1739,8 +2029,10 @@
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H140" s="1"/>
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -1748,8 +2040,10 @@
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H141" s="1"/>
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -1757,8 +2051,10 @@
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H142" s="1"/>
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -1766,8 +2062,10 @@
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H143" s="1"/>
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -1775,8 +2073,10 @@
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -1784,8 +2084,10 @@
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -1793,8 +2095,10 @@
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H146" s="1"/>
+      <c r="I146" s="1"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -1802,8 +2106,10 @@
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H147" s="1"/>
+      <c r="I147" s="1"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -1811,8 +2117,10 @@
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H148" s="1"/>
+      <c r="I148" s="1"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -1820,8 +2128,10 @@
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H149" s="1"/>
+      <c r="I149" s="1"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -1829,8 +2139,10 @@
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H150" s="1"/>
+      <c r="I150" s="1"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -1838,8 +2150,10 @@
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H151" s="1"/>
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -1847,8 +2161,10 @@
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H152" s="1"/>
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -1856,8 +2172,10 @@
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H153" s="1"/>
+      <c r="I153" s="1"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -1865,8 +2183,10 @@
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H154" s="1"/>
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -1874,8 +2194,10 @@
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -1883,8 +2205,10 @@
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H156" s="1"/>
+      <c r="I156" s="1"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -1892,8 +2216,10 @@
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H157" s="1"/>
+      <c r="I157" s="1"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -1901,8 +2227,10 @@
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H158" s="1"/>
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -1910,8 +2238,10 @@
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H159" s="1"/>
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -1919,8 +2249,10 @@
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -1928,8 +2260,10 @@
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -1937,8 +2271,10 @@
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H162" s="1"/>
+      <c r="I162" s="1"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -1946,8 +2282,10 @@
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H163" s="1"/>
+      <c r="I163" s="1"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -1955,8 +2293,10 @@
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H164" s="1"/>
+      <c r="I164" s="1"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -1964,8 +2304,10 @@
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H165" s="1"/>
+      <c r="I165" s="1"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -1973,8 +2315,10 @@
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H166" s="1"/>
+      <c r="I166" s="1"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -1982,8 +2326,10 @@
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H167" s="1"/>
+      <c r="I167" s="1"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -1991,8 +2337,10 @@
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H168" s="1"/>
+      <c r="I168" s="1"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -2000,8 +2348,10 @@
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H169" s="1"/>
+      <c r="I169" s="1"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -2009,8 +2359,10 @@
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H170" s="1"/>
+      <c r="I170" s="1"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -2018,8 +2370,10 @@
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H171" s="1"/>
+      <c r="I171" s="1"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -2027,8 +2381,10 @@
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H172" s="1"/>
+      <c r="I172" s="1"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -2036,8 +2392,10 @@
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H173" s="1"/>
+      <c r="I173" s="1"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -2045,8 +2403,10 @@
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H174" s="1"/>
+      <c r="I174" s="1"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -2054,8 +2414,10 @@
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H175" s="1"/>
+      <c r="I175" s="1"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -2063,8 +2425,10 @@
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H176" s="1"/>
+      <c r="I176" s="1"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -2072,8 +2436,10 @@
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H177" s="1"/>
+      <c r="I177" s="1"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -2081,8 +2447,10 @@
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H178" s="1"/>
+      <c r="I178" s="1"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -2090,8 +2458,10 @@
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H179" s="1"/>
+      <c r="I179" s="1"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -2099,8 +2469,10 @@
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H180" s="1"/>
+      <c r="I180" s="1"/>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -2108,8 +2480,10 @@
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H181" s="1"/>
+      <c r="I181" s="1"/>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -2117,8 +2491,10 @@
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H182" s="1"/>
+      <c r="I182" s="1"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -2126,8 +2502,10 @@
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H183" s="1"/>
+      <c r="I183" s="1"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -2135,8 +2513,10 @@
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -2144,8 +2524,10 @@
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H185" s="1"/>
+      <c r="I185" s="1"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -2153,8 +2535,10 @@
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H186" s="1"/>
+      <c r="I186" s="1"/>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -2162,8 +2546,10 @@
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H187" s="1"/>
+      <c r="I187" s="1"/>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -2171,8 +2557,10 @@
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H188" s="1"/>
+      <c r="I188" s="1"/>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -2180,8 +2568,10 @@
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H189" s="1"/>
+      <c r="I189" s="1"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -2189,8 +2579,10 @@
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H190" s="1"/>
+      <c r="I190" s="1"/>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -2198,8 +2590,10 @@
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H191" s="1"/>
+      <c r="I191" s="1"/>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -2207,8 +2601,10 @@
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H192" s="1"/>
+      <c r="I192" s="1"/>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -2216,8 +2612,10 @@
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H193" s="1"/>
+      <c r="I193" s="1"/>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -2225,8 +2623,10 @@
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H194" s="1"/>
+      <c r="I194" s="1"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -2234,8 +2634,10 @@
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H195" s="1"/>
+      <c r="I195" s="1"/>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -2243,8 +2645,10 @@
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H196" s="1"/>
+      <c r="I196" s="1"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -2252,8 +2656,10 @@
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H197" s="1"/>
+      <c r="I197" s="1"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -2261,8 +2667,10 @@
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H198" s="1"/>
+      <c r="I198" s="1"/>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -2270,8 +2678,10 @@
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H199" s="1"/>
+      <c r="I199" s="1"/>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -2279,8 +2689,10 @@
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H200" s="1"/>
+      <c r="I200" s="1"/>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -2288,8 +2700,10 @@
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H201" s="1"/>
+      <c r="I201" s="1"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -2297,8 +2711,10 @@
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H202" s="1"/>
+      <c r="I202" s="1"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -2306,8 +2722,10 @@
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H203" s="1"/>
+      <c r="I203" s="1"/>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -2315,8 +2733,10 @@
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H204" s="1"/>
+      <c r="I204" s="1"/>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -2324,8 +2744,10 @@
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H205" s="1"/>
+      <c r="I205" s="1"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -2333,8 +2755,10 @@
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H206" s="1"/>
+      <c r="I206" s="1"/>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -2342,8 +2766,10 @@
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H207" s="1"/>
+      <c r="I207" s="1"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -2351,8 +2777,10 @@
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H208" s="1"/>
+      <c r="I208" s="1"/>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -2360,8 +2788,10 @@
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H209" s="1"/>
+      <c r="I209" s="1"/>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -2369,8 +2799,10 @@
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H210" s="1"/>
+      <c r="I210" s="1"/>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -2378,8 +2810,10 @@
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H211" s="1"/>
+      <c r="I211" s="1"/>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -2387,8 +2821,10 @@
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H212" s="1"/>
+      <c r="I212" s="1"/>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -2396,8 +2832,10 @@
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H213" s="1"/>
+      <c r="I213" s="1"/>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -2405,8 +2843,10 @@
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H214" s="1"/>
+      <c r="I214" s="1"/>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -2414,8 +2854,10 @@
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H215" s="1"/>
+      <c r="I215" s="1"/>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -2423,8 +2865,10 @@
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H216" s="1"/>
+      <c r="I216" s="1"/>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -2432,8 +2876,10 @@
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H217" s="1"/>
+      <c r="I217" s="1"/>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -2441,8 +2887,10 @@
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H218" s="1"/>
+      <c r="I218" s="1"/>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -2450,8 +2898,10 @@
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H219" s="1"/>
+      <c r="I219" s="1"/>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -2459,8 +2909,10 @@
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H220" s="1"/>
+      <c r="I220" s="1"/>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -2468,8 +2920,10 @@
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H221" s="1"/>
+      <c r="I221" s="1"/>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -2477,8 +2931,10 @@
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H222" s="1"/>
+      <c r="I222" s="1"/>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -2486,8 +2942,10 @@
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -2495,8 +2953,10 @@
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H224" s="1"/>
+      <c r="I224" s="1"/>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -2504,8 +2964,10 @@
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -2513,8 +2975,10 @@
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -2522,8 +2986,10 @@
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H227" s="1"/>
+      <c r="I227" s="1"/>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -2531,8 +2997,10 @@
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -2540,8 +3008,10 @@
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -2549,8 +3019,10 @@
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -2558,8 +3030,10 @@
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H231" s="1"/>
+      <c r="I231" s="1"/>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -2567,8 +3041,10 @@
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H232" s="1"/>
+      <c r="I232" s="1"/>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -2576,8 +3052,10 @@
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H233" s="1"/>
+      <c r="I233" s="1"/>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -2585,8 +3063,10 @@
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -2594,8 +3074,10 @@
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -2603,8 +3085,10 @@
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H236" s="1"/>
+      <c r="I236" s="1"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -2612,8 +3096,10 @@
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -2621,8 +3107,10 @@
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -2630,8 +3118,10 @@
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -2639,8 +3129,10 @@
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -2648,8 +3140,10 @@
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H241" s="1"/>
+      <c r="I241" s="1"/>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -2657,8 +3151,10 @@
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H242" s="1"/>
+      <c r="I242" s="1"/>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -2666,8 +3162,10 @@
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -2675,8 +3173,10 @@
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H244" s="1"/>
+      <c r="I244" s="1"/>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -2684,8 +3184,10 @@
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H245" s="1"/>
+      <c r="I245" s="1"/>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -2693,8 +3195,10 @@
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H246" s="1"/>
+      <c r="I246" s="1"/>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -2702,8 +3206,10 @@
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H247" s="1"/>
+      <c r="I247" s="1"/>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -2711,8 +3217,10 @@
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H248" s="1"/>
+      <c r="I248" s="1"/>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -2720,8 +3228,10 @@
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H249" s="1"/>
+      <c r="I249" s="1"/>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -2729,8 +3239,10 @@
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H250" s="1"/>
+      <c r="I250" s="1"/>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -2738,8 +3250,10 @@
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H251" s="1"/>
+      <c r="I251" s="1"/>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -2747,8 +3261,10 @@
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H252" s="1"/>
+      <c r="I252" s="1"/>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -2756,8 +3272,10 @@
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -2765,8 +3283,10 @@
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="1"/>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H254" s="1"/>
+      <c r="I254" s="1"/>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -2774,8 +3294,10 @@
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H255" s="1"/>
+      <c r="I255" s="1"/>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -2783,8 +3305,10 @@
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -2792,8 +3316,10 @@
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -2801,8 +3327,10 @@
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -2810,8 +3338,10 @@
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H259" s="1"/>
+      <c r="I259" s="1"/>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -2819,8 +3349,10 @@
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -2828,8 +3360,10 @@
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -2837,8 +3371,10 @@
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -2846,8 +3382,10 @@
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -2855,8 +3393,10 @@
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -2864,8 +3404,10 @@
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H265" s="1"/>
+      <c r="I265" s="1"/>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -2873,8 +3415,10 @@
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H266" s="1"/>
+      <c r="I266" s="1"/>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -2882,8 +3426,10 @@
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H267" s="1"/>
+      <c r="I267" s="1"/>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -2891,8 +3437,10 @@
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H268" s="1"/>
+      <c r="I268" s="1"/>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -2900,8 +3448,10 @@
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H269" s="1"/>
+      <c r="I269" s="1"/>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -2909,8 +3459,10 @@
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H270" s="1"/>
+      <c r="I270" s="1"/>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -2918,8 +3470,10 @@
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H271" s="1"/>
+      <c r="I271" s="1"/>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -2927,8 +3481,10 @@
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H272" s="1"/>
+      <c r="I272" s="1"/>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -2936,8 +3492,10 @@
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -2945,8 +3503,10 @@
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H274" s="1"/>
+      <c r="I274" s="1"/>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -2954,8 +3514,10 @@
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H275" s="1"/>
+      <c r="I275" s="1"/>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -2963,8 +3525,10 @@
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H276" s="1"/>
+      <c r="I276" s="1"/>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -2972,8 +3536,10 @@
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -2981,8 +3547,10 @@
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -2990,8 +3558,10 @@
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -2999,8 +3569,10 @@
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H280" s="1"/>
+      <c r="I280" s="1"/>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -3008,8 +3580,10 @@
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1"/>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H281" s="1"/>
+      <c r="I281" s="1"/>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -3017,8 +3591,10 @@
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="1"/>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -3026,8 +3602,10 @@
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H283" s="1"/>
+      <c r="I283" s="1"/>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -3035,8 +3613,10 @@
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H284" s="1"/>
+      <c r="I284" s="1"/>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -3044,8 +3624,10 @@
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H285" s="1"/>
+      <c r="I285" s="1"/>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -3053,8 +3635,10 @@
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H286" s="1"/>
+      <c r="I286" s="1"/>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -3062,8 +3646,10 @@
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H287" s="1"/>
+      <c r="I287" s="1"/>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -3071,8 +3657,10 @@
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H288" s="1"/>
+      <c r="I288" s="1"/>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -3080,8 +3668,10 @@
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H289" s="1"/>
+      <c r="I289" s="1"/>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -3089,8 +3679,10 @@
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H290" s="1"/>
+      <c r="I290" s="1"/>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -3098,8 +3690,10 @@
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H291" s="1"/>
+      <c r="I291" s="1"/>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -3107,8 +3701,10 @@
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H292" s="1"/>
+      <c r="I292" s="1"/>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -3116,8 +3712,10 @@
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H293" s="1"/>
+      <c r="I293" s="1"/>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -3125,8 +3723,10 @@
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="1"/>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H294" s="1"/>
+      <c r="I294" s="1"/>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -3134,8 +3734,10 @@
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H295" s="1"/>
+      <c r="I295" s="1"/>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -3143,8 +3745,10 @@
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H296" s="1"/>
+      <c r="I296" s="1"/>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -3152,8 +3756,10 @@
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H297" s="1"/>
+      <c r="I297" s="1"/>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -3161,8 +3767,10 @@
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H298" s="1"/>
+      <c r="I298" s="1"/>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -3170,8 +3778,10 @@
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H299" s="1"/>
+      <c r="I299" s="1"/>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -3179,8 +3789,10 @@
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H300" s="1"/>
+      <c r="I300" s="1"/>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -3188,8 +3800,10 @@
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H301" s="1"/>
+      <c r="I301" s="1"/>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -3197,8 +3811,10 @@
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="1"/>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H302" s="1"/>
+      <c r="I302" s="1"/>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -3206,8 +3822,10 @@
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H303" s="1"/>
+      <c r="I303" s="1"/>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -3215,8 +3833,10 @@
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H304" s="1"/>
+      <c r="I304" s="1"/>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -3224,8 +3844,10 @@
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H305" s="1"/>
+      <c r="I305" s="1"/>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -3233,8 +3855,10 @@
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H306" s="1"/>
+      <c r="I306" s="1"/>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -3242,8 +3866,10 @@
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H307" s="1"/>
+      <c r="I307" s="1"/>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -3251,8 +3877,10 @@
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H308" s="1"/>
+      <c r="I308" s="1"/>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -3260,8 +3888,10 @@
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H309" s="1"/>
+      <c r="I309" s="1"/>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -3269,8 +3899,10 @@
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H310" s="1"/>
+      <c r="I310" s="1"/>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -3278,8 +3910,10 @@
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H311" s="1"/>
+      <c r="I311" s="1"/>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -3287,8 +3921,10 @@
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H312" s="1"/>
+      <c r="I312" s="1"/>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -3296,8 +3932,10 @@
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H313" s="1"/>
+      <c r="I313" s="1"/>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -3305,8 +3943,10 @@
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H314" s="1"/>
+      <c r="I314" s="1"/>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -3314,8 +3954,10 @@
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H315" s="1"/>
+      <c r="I315" s="1"/>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -3323,8 +3965,10 @@
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H316" s="1"/>
+      <c r="I316" s="1"/>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -3332,8 +3976,10 @@
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H317" s="1"/>
+      <c r="I317" s="1"/>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -3341,8 +3987,10 @@
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H318" s="1"/>
+      <c r="I318" s="1"/>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -3350,8 +3998,10 @@
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H319" s="1"/>
+      <c r="I319" s="1"/>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -3359,8 +4009,10 @@
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H320" s="1"/>
+      <c r="I320" s="1"/>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -3368,8 +4020,10 @@
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H321" s="1"/>
+      <c r="I321" s="1"/>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -3377,8 +4031,10 @@
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H322" s="1"/>
+      <c r="I322" s="1"/>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -3386,8 +4042,10 @@
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H323" s="1"/>
+      <c r="I323" s="1"/>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -3395,8 +4053,10 @@
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H324" s="1"/>
+      <c r="I324" s="1"/>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -3404,8 +4064,10 @@
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H325" s="1"/>
+      <c r="I325" s="1"/>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -3413,8 +4075,10 @@
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H326" s="1"/>
+      <c r="I326" s="1"/>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -3422,8 +4086,10 @@
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H327" s="1"/>
+      <c r="I327" s="1"/>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -3431,8 +4097,10 @@
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H328" s="1"/>
+      <c r="I328" s="1"/>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -3440,8 +4108,10 @@
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H329" s="1"/>
+      <c r="I329" s="1"/>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -3449,8 +4119,10 @@
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H330" s="1"/>
+      <c r="I330" s="1"/>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -3458,8 +4130,10 @@
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H331" s="1"/>
+      <c r="I331" s="1"/>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -3467,8 +4141,10 @@
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H332" s="1"/>
+      <c r="I332" s="1"/>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -3476,8 +4152,10 @@
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H333" s="1"/>
+      <c r="I333" s="1"/>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -3485,8 +4163,10 @@
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H334" s="1"/>
+      <c r="I334" s="1"/>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -3494,8 +4174,10 @@
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H335" s="1"/>
+      <c r="I335" s="1"/>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -3503,8 +4185,10 @@
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H336" s="1"/>
+      <c r="I336" s="1"/>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -3512,8 +4196,10 @@
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H337" s="1"/>
+      <c r="I337" s="1"/>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -3521,8 +4207,10 @@
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H338" s="1"/>
+      <c r="I338" s="1"/>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -3530,8 +4218,10 @@
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H339" s="1"/>
+      <c r="I339" s="1"/>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -3539,8 +4229,10 @@
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H340" s="1"/>
+      <c r="I340" s="1"/>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -3548,8 +4240,10 @@
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H341" s="1"/>
+      <c r="I341" s="1"/>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -3557,8 +4251,10 @@
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H342" s="1"/>
+      <c r="I342" s="1"/>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -3566,8 +4262,10 @@
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H343" s="1"/>
+      <c r="I343" s="1"/>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -3575,8 +4273,10 @@
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H344" s="1"/>
+      <c r="I344" s="1"/>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -3584,8 +4284,10 @@
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H345" s="1"/>
+      <c r="I345" s="1"/>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -3593,8 +4295,10 @@
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H346" s="1"/>
+      <c r="I346" s="1"/>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -3602,8 +4306,10 @@
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H347" s="1"/>
+      <c r="I347" s="1"/>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -3611,8 +4317,10 @@
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H348" s="1"/>
+      <c r="I348" s="1"/>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -3620,8 +4328,10 @@
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H349" s="1"/>
+      <c r="I349" s="1"/>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -3629,8 +4339,10 @@
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H350" s="1"/>
+      <c r="I350" s="1"/>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -3638,8 +4350,10 @@
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H351" s="1"/>
+      <c r="I351" s="1"/>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -3647,8 +4361,10 @@
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H352" s="1"/>
+      <c r="I352" s="1"/>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -3656,8 +4372,10 @@
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H353" s="1"/>
+      <c r="I353" s="1"/>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -3665,8 +4383,10 @@
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H354" s="1"/>
+      <c r="I354" s="1"/>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -3674,8 +4394,10 @@
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H355" s="1"/>
+      <c r="I355" s="1"/>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -3683,8 +4405,10 @@
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H356" s="1"/>
+      <c r="I356" s="1"/>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -3692,8 +4416,10 @@
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H357" s="1"/>
+      <c r="I357" s="1"/>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -3701,8 +4427,10 @@
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H358" s="1"/>
+      <c r="I358" s="1"/>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -3710,8 +4438,10 @@
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H359" s="1"/>
+      <c r="I359" s="1"/>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -3719,8 +4449,10 @@
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H360" s="1"/>
+      <c r="I360" s="1"/>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -3728,8 +4460,10 @@
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H361" s="1"/>
+      <c r="I361" s="1"/>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -3737,8 +4471,10 @@
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H362" s="1"/>
+      <c r="I362" s="1"/>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -3746,8 +4482,10 @@
       <c r="E363" s="1"/>
       <c r="F363" s="1"/>
       <c r="G363" s="1"/>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H363" s="1"/>
+      <c r="I363" s="1"/>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -3755,8 +4493,10 @@
       <c r="E364" s="1"/>
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H364" s="1"/>
+      <c r="I364" s="1"/>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -3764,8 +4504,10 @@
       <c r="E365" s="1"/>
       <c r="F365" s="1"/>
       <c r="G365" s="1"/>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H365" s="1"/>
+      <c r="I365" s="1"/>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -3773,8 +4515,10 @@
       <c r="E366" s="1"/>
       <c r="F366" s="1"/>
       <c r="G366" s="1"/>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H366" s="1"/>
+      <c r="I366" s="1"/>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -3782,8 +4526,10 @@
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H367" s="1"/>
+      <c r="I367" s="1"/>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -3791,8 +4537,10 @@
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1"/>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H368" s="1"/>
+      <c r="I368" s="1"/>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -3800,8 +4548,10 @@
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H369" s="1"/>
+      <c r="I369" s="1"/>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -3809,8 +4559,10 @@
       <c r="E370" s="1"/>
       <c r="F370" s="1"/>
       <c r="G370" s="1"/>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H370" s="1"/>
+      <c r="I370" s="1"/>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -3818,8 +4570,10 @@
       <c r="E371" s="1"/>
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H371" s="1"/>
+      <c r="I371" s="1"/>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -3827,8 +4581,10 @@
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H372" s="1"/>
+      <c r="I372" s="1"/>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -3836,8 +4592,10 @@
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1"/>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H373" s="1"/>
+      <c r="I373" s="1"/>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -3845,8 +4603,10 @@
       <c r="E374" s="1"/>
       <c r="F374" s="1"/>
       <c r="G374" s="1"/>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H374" s="1"/>
+      <c r="I374" s="1"/>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -3854,8 +4614,10 @@
       <c r="E375" s="1"/>
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H375" s="1"/>
+      <c r="I375" s="1"/>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -3863,8 +4625,10 @@
       <c r="E376" s="1"/>
       <c r="F376" s="1"/>
       <c r="G376" s="1"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H376" s="1"/>
+      <c r="I376" s="1"/>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -3872,8 +4636,10 @@
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H377" s="1"/>
+      <c r="I377" s="1"/>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -3881,8 +4647,10 @@
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1"/>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H378" s="1"/>
+      <c r="I378" s="1"/>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -3890,8 +4658,10 @@
       <c r="E379" s="1"/>
       <c r="F379" s="1"/>
       <c r="G379" s="1"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H379" s="1"/>
+      <c r="I379" s="1"/>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -3899,8 +4669,10 @@
       <c r="E380" s="1"/>
       <c r="F380" s="1"/>
       <c r="G380" s="1"/>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H380" s="1"/>
+      <c r="I380" s="1"/>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -3908,8 +4680,10 @@
       <c r="E381" s="1"/>
       <c r="F381" s="1"/>
       <c r="G381" s="1"/>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H381" s="1"/>
+      <c r="I381" s="1"/>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -3917,8 +4691,10 @@
       <c r="E382" s="1"/>
       <c r="F382" s="1"/>
       <c r="G382" s="1"/>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H382" s="1"/>
+      <c r="I382" s="1"/>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -3926,8 +4702,10 @@
       <c r="E383" s="1"/>
       <c r="F383" s="1"/>
       <c r="G383" s="1"/>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H383" s="1"/>
+      <c r="I383" s="1"/>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -3935,8 +4713,10 @@
       <c r="E384" s="1"/>
       <c r="F384" s="1"/>
       <c r="G384" s="1"/>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H384" s="1"/>
+      <c r="I384" s="1"/>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -3944,8 +4724,10 @@
       <c r="E385" s="1"/>
       <c r="F385" s="1"/>
       <c r="G385" s="1"/>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H385" s="1"/>
+      <c r="I385" s="1"/>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -3953,8 +4735,10 @@
       <c r="E386" s="1"/>
       <c r="F386" s="1"/>
       <c r="G386" s="1"/>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H386" s="1"/>
+      <c r="I386" s="1"/>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -3962,8 +4746,10 @@
       <c r="E387" s="1"/>
       <c r="F387" s="1"/>
       <c r="G387" s="1"/>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H387" s="1"/>
+      <c r="I387" s="1"/>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -3971,8 +4757,10 @@
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H388" s="1"/>
+      <c r="I388" s="1"/>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -3980,8 +4768,10 @@
       <c r="E389" s="1"/>
       <c r="F389" s="1"/>
       <c r="G389" s="1"/>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H389" s="1"/>
+      <c r="I389" s="1"/>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -3989,8 +4779,10 @@
       <c r="E390" s="1"/>
       <c r="F390" s="1"/>
       <c r="G390" s="1"/>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H390" s="1"/>
+      <c r="I390" s="1"/>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -3998,8 +4790,10 @@
       <c r="E391" s="1"/>
       <c r="F391" s="1"/>
       <c r="G391" s="1"/>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H391" s="1"/>
+      <c r="I391" s="1"/>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -4007,8 +4801,10 @@
       <c r="E392" s="1"/>
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H392" s="1"/>
+      <c r="I392" s="1"/>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -4016,8 +4812,10 @@
       <c r="E393" s="1"/>
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H393" s="1"/>
+      <c r="I393" s="1"/>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -4025,8 +4823,10 @@
       <c r="E394" s="1"/>
       <c r="F394" s="1"/>
       <c r="G394" s="1"/>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H394" s="1"/>
+      <c r="I394" s="1"/>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -4034,8 +4834,10 @@
       <c r="E395" s="1"/>
       <c r="F395" s="1"/>
       <c r="G395" s="1"/>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H395" s="1"/>
+      <c r="I395" s="1"/>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -4043,8 +4845,10 @@
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1"/>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H396" s="1"/>
+      <c r="I396" s="1"/>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -4052,8 +4856,10 @@
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1"/>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H397" s="1"/>
+      <c r="I397" s="1"/>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -4061,8 +4867,10 @@
       <c r="E398" s="1"/>
       <c r="F398" s="1"/>
       <c r="G398" s="1"/>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H398" s="1"/>
+      <c r="I398" s="1"/>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -4070,8 +4878,10 @@
       <c r="E399" s="1"/>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H399" s="1"/>
+      <c r="I399" s="1"/>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -4079,8 +4889,10 @@
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H400" s="1"/>
+      <c r="I400" s="1"/>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -4088,8 +4900,10 @@
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1"/>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H401" s="1"/>
+      <c r="I401" s="1"/>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -4097,8 +4911,10 @@
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1"/>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H402" s="1"/>
+      <c r="I402" s="1"/>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -4106,8 +4922,10 @@
       <c r="E403" s="1"/>
       <c r="F403" s="1"/>
       <c r="G403" s="1"/>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H403" s="1"/>
+      <c r="I403" s="1"/>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -4115,8 +4933,10 @@
       <c r="E404" s="1"/>
       <c r="F404" s="1"/>
       <c r="G404" s="1"/>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H404" s="1"/>
+      <c r="I404" s="1"/>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -4124,8 +4944,10 @@
       <c r="E405" s="1"/>
       <c r="F405" s="1"/>
       <c r="G405" s="1"/>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H405" s="1"/>
+      <c r="I405" s="1"/>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -4133,8 +4955,10 @@
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1"/>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H406" s="1"/>
+      <c r="I406" s="1"/>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -4142,8 +4966,10 @@
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1"/>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H407" s="1"/>
+      <c r="I407" s="1"/>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -4151,8 +4977,10 @@
       <c r="E408" s="1"/>
       <c r="F408" s="1"/>
       <c r="G408" s="1"/>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H408" s="1"/>
+      <c r="I408" s="1"/>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -4160,8 +4988,10 @@
       <c r="E409" s="1"/>
       <c r="F409" s="1"/>
       <c r="G409" s="1"/>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H409" s="1"/>
+      <c r="I409" s="1"/>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -4169,8 +4999,10 @@
       <c r="E410" s="1"/>
       <c r="F410" s="1"/>
       <c r="G410" s="1"/>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H410" s="1"/>
+      <c r="I410" s="1"/>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -4178,8 +5010,10 @@
       <c r="E411" s="1"/>
       <c r="F411" s="1"/>
       <c r="G411" s="1"/>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H411" s="1"/>
+      <c r="I411" s="1"/>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -4187,8 +5021,10 @@
       <c r="E412" s="1"/>
       <c r="F412" s="1"/>
       <c r="G412" s="1"/>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H412" s="1"/>
+      <c r="I412" s="1"/>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -4196,8 +5032,10 @@
       <c r="E413" s="1"/>
       <c r="F413" s="1"/>
       <c r="G413" s="1"/>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H413" s="1"/>
+      <c r="I413" s="1"/>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -4205,8 +5043,10 @@
       <c r="E414" s="1"/>
       <c r="F414" s="1"/>
       <c r="G414" s="1"/>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H414" s="1"/>
+      <c r="I414" s="1"/>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -4214,8 +5054,10 @@
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
       <c r="G415" s="1"/>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H415" s="1"/>
+      <c r="I415" s="1"/>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -4223,8 +5065,10 @@
       <c r="E416" s="1"/>
       <c r="F416" s="1"/>
       <c r="G416" s="1"/>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H416" s="1"/>
+      <c r="I416" s="1"/>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -4232,8 +5076,10 @@
       <c r="E417" s="1"/>
       <c r="F417" s="1"/>
       <c r="G417" s="1"/>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H417" s="1"/>
+      <c r="I417" s="1"/>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -4241,8 +5087,10 @@
       <c r="E418" s="1"/>
       <c r="F418" s="1"/>
       <c r="G418" s="1"/>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H418" s="1"/>
+      <c r="I418" s="1"/>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -4250,8 +5098,10 @@
       <c r="E419" s="1"/>
       <c r="F419" s="1"/>
       <c r="G419" s="1"/>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H419" s="1"/>
+      <c r="I419" s="1"/>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -4259,8 +5109,10 @@
       <c r="E420" s="1"/>
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H420" s="1"/>
+      <c r="I420" s="1"/>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -4268,8 +5120,10 @@
       <c r="E421" s="1"/>
       <c r="F421" s="1"/>
       <c r="G421" s="1"/>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H421" s="1"/>
+      <c r="I421" s="1"/>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -4277,8 +5131,10 @@
       <c r="E422" s="1"/>
       <c r="F422" s="1"/>
       <c r="G422" s="1"/>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H422" s="1"/>
+      <c r="I422" s="1"/>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -4286,8 +5142,10 @@
       <c r="E423" s="1"/>
       <c r="F423" s="1"/>
       <c r="G423" s="1"/>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H423" s="1"/>
+      <c r="I423" s="1"/>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -4295,8 +5153,10 @@
       <c r="E424" s="1"/>
       <c r="F424" s="1"/>
       <c r="G424" s="1"/>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H424" s="1"/>
+      <c r="I424" s="1"/>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -4304,8 +5164,10 @@
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1"/>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H425" s="1"/>
+      <c r="I425" s="1"/>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -4313,8 +5175,10 @@
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1"/>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H426" s="1"/>
+      <c r="I426" s="1"/>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -4322,8 +5186,10 @@
       <c r="E427" s="1"/>
       <c r="F427" s="1"/>
       <c r="G427" s="1"/>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H427" s="1"/>
+      <c r="I427" s="1"/>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -4331,8 +5197,10 @@
       <c r="E428" s="1"/>
       <c r="F428" s="1"/>
       <c r="G428" s="1"/>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H428" s="1"/>
+      <c r="I428" s="1"/>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -4340,8 +5208,10 @@
       <c r="E429" s="1"/>
       <c r="F429" s="1"/>
       <c r="G429" s="1"/>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H429" s="1"/>
+      <c r="I429" s="1"/>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -4349,8 +5219,10 @@
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1"/>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H430" s="1"/>
+      <c r="I430" s="1"/>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -4358,8 +5230,10 @@
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1"/>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H431" s="1"/>
+      <c r="I431" s="1"/>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -4367,8 +5241,10 @@
       <c r="E432" s="1"/>
       <c r="F432" s="1"/>
       <c r="G432" s="1"/>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H432" s="1"/>
+      <c r="I432" s="1"/>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -4376,8 +5252,10 @@
       <c r="E433" s="1"/>
       <c r="F433" s="1"/>
       <c r="G433" s="1"/>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H433" s="1"/>
+      <c r="I433" s="1"/>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -4385,8 +5263,10 @@
       <c r="E434" s="1"/>
       <c r="F434" s="1"/>
       <c r="G434" s="1"/>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H434" s="1"/>
+      <c r="I434" s="1"/>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -4394,8 +5274,10 @@
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1"/>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H435" s="1"/>
+      <c r="I435" s="1"/>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -4403,8 +5285,10 @@
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
       <c r="G436" s="1"/>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H436" s="1"/>
+      <c r="I436" s="1"/>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -4412,8 +5296,10 @@
       <c r="E437" s="1"/>
       <c r="F437" s="1"/>
       <c r="G437" s="1"/>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H437" s="1"/>
+      <c r="I437" s="1"/>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -4421,8 +5307,10 @@
       <c r="E438" s="1"/>
       <c r="F438" s="1"/>
       <c r="G438" s="1"/>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H438" s="1"/>
+      <c r="I438" s="1"/>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -4430,8 +5318,10 @@
       <c r="E439" s="1"/>
       <c r="F439" s="1"/>
       <c r="G439" s="1"/>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H439" s="1"/>
+      <c r="I439" s="1"/>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -4439,8 +5329,10 @@
       <c r="E440" s="1"/>
       <c r="F440" s="1"/>
       <c r="G440" s="1"/>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H440" s="1"/>
+      <c r="I440" s="1"/>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -4448,8 +5340,10 @@
       <c r="E441" s="1"/>
       <c r="F441" s="1"/>
       <c r="G441" s="1"/>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H441" s="1"/>
+      <c r="I441" s="1"/>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -4457,8 +5351,10 @@
       <c r="E442" s="1"/>
       <c r="F442" s="1"/>
       <c r="G442" s="1"/>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H442" s="1"/>
+      <c r="I442" s="1"/>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -4466,8 +5362,10 @@
       <c r="E443" s="1"/>
       <c r="F443" s="1"/>
       <c r="G443" s="1"/>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H443" s="1"/>
+      <c r="I443" s="1"/>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -4475,8 +5373,10 @@
       <c r="E444" s="1"/>
       <c r="F444" s="1"/>
       <c r="G444" s="1"/>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H444" s="1"/>
+      <c r="I444" s="1"/>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -4484,8 +5384,10 @@
       <c r="E445" s="1"/>
       <c r="F445" s="1"/>
       <c r="G445" s="1"/>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H445" s="1"/>
+      <c r="I445" s="1"/>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -4493,8 +5395,10 @@
       <c r="E446" s="1"/>
       <c r="F446" s="1"/>
       <c r="G446" s="1"/>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H446" s="1"/>
+      <c r="I446" s="1"/>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -4502,8 +5406,10 @@
       <c r="E447" s="1"/>
       <c r="F447" s="1"/>
       <c r="G447" s="1"/>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H447" s="1"/>
+      <c r="I447" s="1"/>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -4511,8 +5417,10 @@
       <c r="E448" s="1"/>
       <c r="F448" s="1"/>
       <c r="G448" s="1"/>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H448" s="1"/>
+      <c r="I448" s="1"/>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -4520,8 +5428,10 @@
       <c r="E449" s="1"/>
       <c r="F449" s="1"/>
       <c r="G449" s="1"/>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H449" s="1"/>
+      <c r="I449" s="1"/>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -4529,8 +5439,10 @@
       <c r="E450" s="1"/>
       <c r="F450" s="1"/>
       <c r="G450" s="1"/>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H450" s="1"/>
+      <c r="I450" s="1"/>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -4538,8 +5450,10 @@
       <c r="E451" s="1"/>
       <c r="F451" s="1"/>
       <c r="G451" s="1"/>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H451" s="1"/>
+      <c r="I451" s="1"/>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -4547,8 +5461,10 @@
       <c r="E452" s="1"/>
       <c r="F452" s="1"/>
       <c r="G452" s="1"/>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H452" s="1"/>
+      <c r="I452" s="1"/>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -4556,16 +5472,20 @@
       <c r="E453" s="1"/>
       <c r="F453" s="1"/>
       <c r="G453" s="1"/>
+      <c r="H453" s="1"/>
+      <c r="I453" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="D2:E2"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
